--- a/03_Labeling/outputs/full_annotation/full_annotation_381.xlsx
+++ b/03_Labeling/outputs/full_annotation/full_annotation_381.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Penelitian Sentimen Bencana Nasional\03_Labeling\outputs\full_annotation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0EEC4A-7C39-4048-B6FA-65C63BCC2496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FFB09E0-5C95-49DF-8E06-D822E1E46F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4737" uniqueCount="2188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4745" uniqueCount="2190">
   <si>
     <t>Topic</t>
   </si>
@@ -7184,6 +7184,12 @@
   </si>
   <si>
     <t>menyatakan informasi belum menjadi bencana nasional dan menyatakan kritik</t>
+  </si>
+  <si>
+    <t>hanya menunjukkkan pandangan pemerintah</t>
+  </si>
+  <si>
+    <t>menyatakan dukungan terhadap penetapan bencana nasional</t>
   </si>
 </sst>
 </file>
@@ -8252,11 +8258,17 @@
         <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>2188</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="P12" s="3" t="s">
         <v>12</v>
       </c>
@@ -9548,7 +9560,9 @@
       <c r="L38" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="3"/>
+      <c r="M38" s="3" t="s">
+        <v>2182</v>
+      </c>
       <c r="N38" s="9" t="s">
         <v>45</v>
       </c>
@@ -10046,7 +10060,9 @@
       <c r="L48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M48" s="3"/>
+      <c r="M48" s="3" t="s">
+        <v>2189</v>
+      </c>
       <c r="N48" s="9" t="s">
         <v>45</v>
       </c>
@@ -10194,7 +10210,9 @@
       <c r="L51" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M51" s="3"/>
+      <c r="M51" s="3" t="s">
+        <v>2189</v>
+      </c>
       <c r="N51" s="9" t="s">
         <v>45</v>
       </c>
@@ -11898,7 +11916,9 @@
       <c r="N85" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="O85" s="3"/>
+      <c r="O85" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="P85" s="3" t="s">
         <v>12</v>
       </c>
@@ -11946,7 +11966,9 @@
       <c r="N86" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="O86" s="3"/>
+      <c r="O86" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="P86" s="3" t="s">
         <v>12</v>
       </c>
@@ -11994,7 +12016,9 @@
       <c r="N87" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="O87" s="3"/>
+      <c r="O87" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="P87" s="3" t="s">
         <v>12</v>
       </c>
@@ -13136,9 +13160,7 @@
       </c>
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
-      <c r="O110" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="O110" s="9"/>
       <c r="P110" s="3" t="s">
         <v>12</v>
       </c>

--- a/03_Labeling/outputs/full_annotation/full_annotation_381.xlsx
+++ b/03_Labeling/outputs/full_annotation/full_annotation_381.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Penelitian Sentimen Bencana Nasional\03_Labeling\outputs\full_annotation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACD8490-9C5D-453C-9D2E-03E600C69E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1689B4-7D61-4651-AAAD-26DF7D3DD769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5277" uniqueCount="2205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5278" uniqueCount="2205">
   <si>
     <t>Topic</t>
   </si>
@@ -18706,7 +18706,9 @@
       <c r="J223" s="3" t="s">
         <v>1281</v>
       </c>
-      <c r="K223" s="3"/>
+      <c r="K223" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="L223" s="3" t="s">
         <v>43</v>
       </c>

--- a/03_Labeling/outputs/full_annotation/full_annotation_381.xlsx
+++ b/03_Labeling/outputs/full_annotation/full_annotation_381.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Penelitian Sentimen Bencana Nasional\03_Labeling\outputs\full_annotation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1689B4-7D61-4651-AAAD-26DF7D3DD769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A9B290-41C0-4EE3-A833-3A941ADDFEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5278" uniqueCount="2205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5498" uniqueCount="2207">
   <si>
     <t>Topic</t>
   </si>
@@ -7236,6 +7236,12 @@
   <si>
     <t>mempertanyakan dan mendesak penetapan bencana sembari melemperkan kritik</t>
   </si>
+  <si>
+    <t>hanya menyampaikan informasi saja</t>
+  </si>
+  <si>
+    <t>menunjukkan penolakan terhadap penetapan status</t>
+  </si>
 </sst>
 </file>
 
@@ -7280,7 +7286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7304,9 +7310,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -7911,10 +7914,10 @@
       <c r="M4" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N4" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O4" s="9" t="s">
+      <c r="N4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P4" s="3" t="s">
@@ -7961,10 +7964,10 @@
       <c r="M5" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="N5" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O5" s="9" t="s">
+      <c r="N5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P5" s="3" t="s">
@@ -8011,10 +8014,10 @@
       <c r="M6" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" s="9" t="s">
+      <c r="N6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P6" s="3" t="s">
@@ -8061,10 +8064,10 @@
       <c r="M7" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="N7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O7" s="9" t="s">
+      <c r="N7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P7" s="3" t="s">
@@ -8111,10 +8114,10 @@
       <c r="M8" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="N8" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O8" s="9" t="s">
+      <c r="N8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P8" s="3" t="s">
@@ -8161,10 +8164,10 @@
       <c r="M9" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="N9" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O9" s="9" t="s">
+      <c r="N9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P9" s="3" t="s">
@@ -8211,10 +8214,10 @@
       <c r="M10" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N10" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O10" s="9" t="s">
+      <c r="N10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P10" s="3" t="s">
@@ -8261,10 +8264,10 @@
       <c r="M11" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N11" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O11" s="9" t="s">
+      <c r="N11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P11" s="3" t="s">
@@ -8311,10 +8314,10 @@
       <c r="M12" s="3" t="s">
         <v>2187</v>
       </c>
-      <c r="N12" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O12" s="9" t="s">
+      <c r="N12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P12" s="3" t="s">
@@ -8361,10 +8364,10 @@
       <c r="M13" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="N13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O13" s="9" t="s">
+      <c r="N13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P13" s="3" t="s">
@@ -8411,10 +8414,10 @@
       <c r="M14" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N14" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O14" s="9" t="s">
+      <c r="N14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P14" s="3" t="s">
@@ -8461,10 +8464,10 @@
       <c r="M15" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N15" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O15" s="9" t="s">
+      <c r="N15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P15" s="3" t="s">
@@ -8511,10 +8514,10 @@
       <c r="M16" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N16" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O16" s="9" t="s">
+      <c r="N16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P16" s="3" t="s">
@@ -8561,10 +8564,10 @@
       <c r="M17" s="3" t="s">
         <v>2185</v>
       </c>
-      <c r="N17" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O17" s="9" t="s">
+      <c r="N17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O17" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P17" s="3" t="s">
@@ -8611,10 +8614,10 @@
       <c r="M18" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N18" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O18" s="9" t="s">
+      <c r="N18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P18" s="3" t="s">
@@ -8661,10 +8664,10 @@
       <c r="M19" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N19" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O19" s="9" t="s">
+      <c r="N19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P19" s="3" t="s">
@@ -8711,10 +8714,10 @@
       <c r="M20" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N20" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O20" s="9" t="s">
+      <c r="N20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P20" s="3" t="s">
@@ -8761,10 +8764,10 @@
       <c r="M21" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="N21" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O21" s="9" t="s">
+      <c r="N21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P21" s="3" t="s">
@@ -8811,10 +8814,10 @@
       <c r="M22" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N22" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O22" s="9" t="s">
+      <c r="N22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P22" s="3" t="s">
@@ -8861,10 +8864,10 @@
       <c r="M23" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N23" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O23" s="9" t="s">
+      <c r="N23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O23" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P23" s="3" t="s">
@@ -8911,10 +8914,10 @@
       <c r="M24" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N24" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O24" s="9" t="s">
+      <c r="N24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P24" s="3" t="s">
@@ -8961,17 +8964,17 @@
       <c r="M25" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N25" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O25" s="9" t="s">
+      <c r="N25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O25" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>167</v>
       </c>
@@ -9011,17 +9014,17 @@
       <c r="M26" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N26" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O26" s="9" t="s">
+      <c r="N26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O26" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>167</v>
       </c>
@@ -9061,10 +9064,10 @@
       <c r="M27" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N27" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O27" s="9" t="s">
+      <c r="N27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O27" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P27" s="3" t="s">
@@ -9111,17 +9114,17 @@
       <c r="M28" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N28" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O28" s="9" t="s">
+      <c r="N28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O28" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>167</v>
       </c>
@@ -9161,10 +9164,10 @@
       <c r="M29" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N29" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O29" s="9" t="s">
+      <c r="N29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O29" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P29" s="3" t="s">
@@ -9211,17 +9214,17 @@
       <c r="M30" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="N30" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O30" s="9" t="s">
+      <c r="N30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O30" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>167</v>
       </c>
@@ -9261,10 +9264,10 @@
       <c r="M31" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N31" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O31" s="9" t="s">
+      <c r="N31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O31" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P31" s="3" t="s">
@@ -9311,10 +9314,10 @@
       <c r="M32" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N32" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O32" s="9" t="s">
+      <c r="N32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O32" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P32" s="3" t="s">
@@ -9361,10 +9364,10 @@
       <c r="M33" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N33" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O33" s="9" t="s">
+      <c r="N33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O33" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P33" s="3" t="s">
@@ -9411,7 +9414,7 @@
       <c r="M34" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N34" s="9" t="s">
+      <c r="N34" s="3" t="s">
         <v>45</v>
       </c>
       <c r="O34" s="2" t="s">
@@ -9461,10 +9464,10 @@
       <c r="M35" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N35" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O35" s="9" t="s">
+      <c r="N35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O35" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P35" s="3" t="s">
@@ -9511,10 +9514,10 @@
       <c r="M36" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N36" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O36" s="9" t="s">
+      <c r="N36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O36" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P36" s="3" t="s">
@@ -9561,10 +9564,10 @@
       <c r="M37" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="N37" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O37" s="9" t="s">
+      <c r="N37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O37" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P37" s="3" t="s">
@@ -9611,10 +9614,10 @@
       <c r="M38" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N38" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O38" s="9" t="s">
+      <c r="N38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O38" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P38" s="3" t="s">
@@ -9661,10 +9664,10 @@
       <c r="M39" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N39" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O39" s="9" t="s">
+      <c r="N39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O39" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P39" s="3" t="s">
@@ -9711,10 +9714,10 @@
       <c r="M40" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N40" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O40" s="9" t="s">
+      <c r="N40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O40" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P40" s="3" t="s">
@@ -9761,10 +9764,10 @@
       <c r="M41" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N41" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O41" s="9" t="s">
+      <c r="N41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O41" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P41" s="3" t="s">
@@ -9811,10 +9814,10 @@
       <c r="M42" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N42" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O42" s="9" t="s">
+      <c r="N42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O42" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P42" s="3" t="s">
@@ -9861,10 +9864,10 @@
       <c r="M43" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N43" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O43" s="9" t="s">
+      <c r="N43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O43" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P43" s="3" t="s">
@@ -9911,10 +9914,10 @@
       <c r="M44" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N44" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O44" s="9" t="s">
+      <c r="N44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O44" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P44" s="3" t="s">
@@ -9961,10 +9964,10 @@
       <c r="M45" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N45" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O45" s="9" t="s">
+      <c r="N45" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O45" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P45" s="3" t="s">
@@ -10011,10 +10014,10 @@
       <c r="M46" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N46" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O46" s="9" t="s">
+      <c r="N46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O46" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P46" s="3" t="s">
@@ -10061,10 +10064,10 @@
       <c r="M47" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N47" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O47" s="9" t="s">
+      <c r="N47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O47" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P47" s="3" t="s">
@@ -10111,10 +10114,10 @@
       <c r="M48" s="3" t="s">
         <v>2188</v>
       </c>
-      <c r="N48" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O48" s="9" t="s">
+      <c r="N48" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O48" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P48" s="3" t="s">
@@ -10161,10 +10164,10 @@
       <c r="M49" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N49" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O49" s="9" t="s">
+      <c r="N49" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O49" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P49" s="3" t="s">
@@ -10211,10 +10214,10 @@
       <c r="M50" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N50" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O50" s="9" t="s">
+      <c r="N50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O50" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P50" s="3" t="s">
@@ -10261,10 +10264,10 @@
       <c r="M51" s="3" t="s">
         <v>2188</v>
       </c>
-      <c r="N51" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O51" s="9" t="s">
+      <c r="N51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O51" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P51" s="3" t="s">
@@ -10311,10 +10314,10 @@
       <c r="M52" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="N52" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O52" s="9" t="s">
+      <c r="N52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O52" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P52" s="3" t="s">
@@ -10361,10 +10364,10 @@
       <c r="M53" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N53" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O53" s="9" t="s">
+      <c r="N53" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O53" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P53" s="3" t="s">
@@ -10461,10 +10464,10 @@
       <c r="M55" s="3" t="s">
         <v>2183</v>
       </c>
-      <c r="N55" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O55" s="9" t="s">
+      <c r="N55" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O55" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P55" s="3" t="s">
@@ -10511,10 +10514,10 @@
       <c r="M56" s="3" t="s">
         <v>2182</v>
       </c>
-      <c r="N56" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O56" s="9" t="s">
+      <c r="N56" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O56" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P56" s="3" t="s">
@@ -10561,10 +10564,10 @@
       <c r="M57" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N57" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O57" s="9" t="s">
+      <c r="N57" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O57" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P57" s="3" t="s">
@@ -10611,10 +10614,10 @@
       <c r="M58" s="3" t="s">
         <v>2184</v>
       </c>
-      <c r="N58" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O58" s="9" t="s">
+      <c r="N58" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O58" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P58" s="3" t="s">
@@ -10661,10 +10664,10 @@
       <c r="M59" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="N59" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O59" s="9" t="s">
+      <c r="N59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O59" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P59" s="3" t="s">
@@ -10711,10 +10714,10 @@
       <c r="M60" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N60" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O60" s="9" t="s">
+      <c r="N60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O60" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P60" s="3" t="s">
@@ -10761,10 +10764,10 @@
       <c r="M61" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N61" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O61" s="9" t="s">
+      <c r="N61" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O61" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P61" s="3" t="s">
@@ -10811,10 +10814,10 @@
       <c r="M62" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N62" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O62" s="9" t="s">
+      <c r="N62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O62" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P62" s="3" t="s">
@@ -10861,10 +10864,10 @@
       <c r="M63" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N63" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O63" s="9" t="s">
+      <c r="N63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O63" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P63" s="3" t="s">
@@ -10911,10 +10914,10 @@
       <c r="M64" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N64" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O64" s="9" t="s">
+      <c r="N64" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O64" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P64" s="3" t="s">
@@ -10961,10 +10964,10 @@
       <c r="M65" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N65" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O65" s="9" t="s">
+      <c r="N65" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O65" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P65" s="3" t="s">
@@ -11011,10 +11014,10 @@
       <c r="M66" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N66" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O66" s="9" t="s">
+      <c r="N66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O66" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P66" s="3" t="s">
@@ -11061,10 +11064,10 @@
       <c r="M67" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N67" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O67" s="9" t="s">
+      <c r="N67" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O67" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P67" s="3" t="s">
@@ -11111,10 +11114,10 @@
       <c r="M68" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N68" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O68" s="9" t="s">
+      <c r="N68" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O68" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P68" s="3" t="s">
@@ -11161,10 +11164,10 @@
       <c r="M69" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N69" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O69" s="9" t="s">
+      <c r="N69" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O69" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P69" s="3" t="s">
@@ -11211,10 +11214,10 @@
       <c r="M70" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="N70" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O70" s="9" t="s">
+      <c r="N70" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O70" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P70" s="3" t="s">
@@ -11261,10 +11264,10 @@
       <c r="M71" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N71" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O71" s="9" t="s">
+      <c r="N71" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O71" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P71" s="3" t="s">
@@ -11311,10 +11314,10 @@
       <c r="M72" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N72" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O72" s="9" t="s">
+      <c r="N72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O72" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P72" s="3" t="s">
@@ -11361,17 +11364,17 @@
       <c r="M73" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N73" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O73" s="9" t="s">
+      <c r="N73" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O73" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P73" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>167</v>
       </c>
@@ -11452,7 +11455,7 @@
       <c r="J75" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K75" s="9" t="s">
+      <c r="K75" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L75" s="3" t="s">
@@ -11461,17 +11464,17 @@
       <c r="M75" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N75" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O75" s="9" t="s">
+      <c r="N75" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O75" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P75" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>167</v>
       </c>
@@ -11502,7 +11505,7 @@
       <c r="J76" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="K76" s="9" t="s">
+      <c r="K76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L76" s="3" t="s">
@@ -11511,17 +11514,17 @@
       <c r="M76" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N76" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O76" s="9" t="s">
+      <c r="N76" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O76" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>167</v>
       </c>
@@ -11552,7 +11555,7 @@
       <c r="J77" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="K77" s="9" t="s">
+      <c r="K77" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L77" s="3" t="s">
@@ -11561,17 +11564,17 @@
       <c r="M77" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N77" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O77" s="9" t="s">
+      <c r="N77" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O77" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P77" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>167</v>
       </c>
@@ -11602,7 +11605,7 @@
       <c r="J78" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="K78" s="9" t="s">
+      <c r="K78" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L78" s="3" t="s">
@@ -11611,10 +11614,10 @@
       <c r="M78" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N78" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O78" s="9" t="s">
+      <c r="N78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O78" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P78" s="3" t="s">
@@ -11652,7 +11655,7 @@
       <c r="J79" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="K79" s="9" t="s">
+      <c r="K79" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L79" s="3" t="s">
@@ -11661,10 +11664,10 @@
       <c r="M79" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N79" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O79" s="9" t="s">
+      <c r="N79" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O79" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P79" s="3" t="s">
@@ -11702,7 +11705,7 @@
       <c r="J80" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="K80" s="9" t="s">
+      <c r="K80" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L80" s="3" t="s">
@@ -11711,10 +11714,10 @@
       <c r="M80" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N80" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O80" s="9" t="s">
+      <c r="N80" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O80" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P80" s="3" t="s">
@@ -11752,7 +11755,7 @@
       <c r="J81" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="K81" s="9" t="s">
+      <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L81" s="3" t="s">
@@ -11761,10 +11764,10 @@
       <c r="M81" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N81" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O81" s="9" t="s">
+      <c r="N81" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O81" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P81" s="3" t="s">
@@ -11802,7 +11805,7 @@
       <c r="J82" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="K82" s="9" t="s">
+      <c r="K82" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L82" s="3" t="s">
@@ -11811,17 +11814,17 @@
       <c r="M82" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N82" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O82" s="9" t="s">
+      <c r="N82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O82" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P82" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>167</v>
       </c>
@@ -11852,7 +11855,7 @@
       <c r="J83" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="K83" s="9" t="s">
+      <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L83" s="3" t="s">
@@ -11861,10 +11864,10 @@
       <c r="M83" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N83" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O83" s="9" t="s">
+      <c r="N83" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O83" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P83" s="3" t="s">
@@ -11961,10 +11964,10 @@
       <c r="M85" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N85" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O85" s="9" t="s">
+      <c r="N85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O85" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P85" s="3" t="s">
@@ -12011,10 +12014,10 @@
       <c r="M86" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N86" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O86" s="9" t="s">
+      <c r="N86" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O86" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P86" s="3" t="s">
@@ -12061,10 +12064,10 @@
       <c r="M87" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N87" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O87" s="9" t="s">
+      <c r="N87" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O87" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P87" s="3" t="s">
@@ -12161,10 +12164,10 @@
       <c r="M89" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N89" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O89" s="9" t="s">
+      <c r="N89" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O89" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P89" s="3" t="s">
@@ -12221,7 +12224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>47</v>
       </c>
@@ -12261,10 +12264,10 @@
       <c r="M91" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N91" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O91" s="9" t="s">
+      <c r="N91" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O91" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P91" s="3" t="s">
@@ -12311,10 +12314,10 @@
       <c r="M92" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N92" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O92" s="9" t="s">
+      <c r="N92" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O92" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P92" s="3" t="s">
@@ -12361,10 +12364,10 @@
       <c r="M93" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N93" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O93" s="9" t="s">
+      <c r="N93" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O93" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P93" s="3" t="s">
@@ -12411,10 +12414,10 @@
       <c r="M94" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N94" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O94" s="9" t="s">
+      <c r="N94" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O94" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P94" s="3" t="s">
@@ -12461,10 +12464,10 @@
       <c r="M95" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N95" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O95" s="9" t="s">
+      <c r="N95" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O95" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P95" s="3" t="s">
@@ -12511,10 +12514,10 @@
       <c r="M96" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N96" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O96" s="9" t="s">
+      <c r="N96" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O96" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P96" s="3" t="s">
@@ -12561,10 +12564,10 @@
       <c r="M97" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N97" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O97" s="9" t="s">
+      <c r="N97" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O97" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P97" s="3" t="s">
@@ -12611,10 +12614,10 @@
       <c r="M98" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N98" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O98" s="9" t="s">
+      <c r="N98" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O98" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P98" s="3" t="s">
@@ -12661,10 +12664,10 @@
       <c r="M99" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N99" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O99" s="9" t="s">
+      <c r="N99" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O99" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P99" s="3" t="s">
@@ -12711,10 +12714,10 @@
       <c r="M100" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N100" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O100" s="9" t="s">
+      <c r="N100" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O100" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P100" s="3" t="s">
@@ -12761,10 +12764,10 @@
       <c r="M101" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N101" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O101" s="9" t="s">
+      <c r="N101" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O101" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P101" s="3" t="s">
@@ -12811,10 +12814,10 @@
       <c r="M102" s="3" t="s">
         <v>2186</v>
       </c>
-      <c r="N102" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O102" s="9" t="s">
+      <c r="N102" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P102" s="3" t="s">
@@ -12861,10 +12864,10 @@
       <c r="M103" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N103" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O103" s="9" t="s">
+      <c r="N103" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O103" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P103" s="3" t="s">
@@ -12911,17 +12914,17 @@
       <c r="M104" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N104" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O104" s="9" t="s">
+      <c r="N104" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O104" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P104" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>34</v>
       </c>
@@ -12961,10 +12964,10 @@
       <c r="M105" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N105" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O105" s="9" t="s">
+      <c r="N105" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O105" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P105" s="3" t="s">
@@ -13011,10 +13014,10 @@
       <c r="M106" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N106" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O106" s="9" t="s">
+      <c r="N106" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O106" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P106" s="3" t="s">
@@ -13061,17 +13064,17 @@
       <c r="M107" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N107" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O107" s="9" t="s">
+      <c r="N107" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O107" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P107" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>34</v>
       </c>
@@ -13111,10 +13114,10 @@
       <c r="M108" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N108" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O108" s="9" t="s">
+      <c r="N108" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O108" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P108" s="3" t="s">
@@ -13161,10 +13164,10 @@
       <c r="M109" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="N109" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O109" s="9" t="s">
+      <c r="N109" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O109" s="3" t="s">
         <v>46</v>
       </c>
       <c r="P109" s="3" t="s">
@@ -13211,10 +13214,10 @@
       <c r="M110" s="3" t="s">
         <v>2181</v>
       </c>
-      <c r="N110" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O110" s="10">
+      <c r="N110" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O110" s="9">
         <v>46313</v>
       </c>
       <c r="P110" s="3" t="s">
@@ -13311,17 +13314,17 @@
       <c r="M112" s="5" t="s">
         <v>2189</v>
       </c>
-      <c r="N112" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O112" s="10">
+      <c r="N112" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O112" s="9">
         <v>46313</v>
       </c>
       <c r="P112" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:16" ht="144" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>167</v>
       </c>
@@ -13361,10 +13364,10 @@
       <c r="M113" s="5" t="s">
         <v>2181</v>
       </c>
-      <c r="N113" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O113" s="10">
+      <c r="N113" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O113" s="9">
         <v>46313</v>
       </c>
       <c r="P113" s="3" t="s">
@@ -13411,10 +13414,10 @@
       <c r="M114" s="5" t="s">
         <v>2190</v>
       </c>
-      <c r="N114" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O114" s="10">
+      <c r="N114" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O114" s="9">
         <v>46313</v>
       </c>
       <c r="P114" s="3" t="s">
@@ -13461,10 +13464,10 @@
       <c r="M115" s="5" t="s">
         <v>2191</v>
       </c>
-      <c r="N115" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O115" s="10">
+      <c r="N115" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O115" s="9">
         <v>46313</v>
       </c>
       <c r="P115" s="3" t="s">
@@ -13511,10 +13514,10 @@
       <c r="M116" s="5" t="s">
         <v>2192</v>
       </c>
-      <c r="N116" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O116" s="10">
+      <c r="N116" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O116" s="9">
         <v>46313</v>
       </c>
       <c r="P116" s="3" t="s">
@@ -13561,10 +13564,10 @@
       <c r="M117" s="5" t="s">
         <v>2193</v>
       </c>
-      <c r="N117" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O117" s="10">
+      <c r="N117" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O117" s="9">
         <v>46313</v>
       </c>
       <c r="P117" s="3" t="s">
@@ -13611,10 +13614,10 @@
       <c r="M118" s="5" t="s">
         <v>2188</v>
       </c>
-      <c r="N118" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O118" s="10">
+      <c r="N118" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O118" s="9">
         <v>46313</v>
       </c>
       <c r="P118" s="3" t="s">
@@ -13661,10 +13664,10 @@
       <c r="M119" s="5" t="s">
         <v>2194</v>
       </c>
-      <c r="N119" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O119" s="10">
+      <c r="N119" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O119" s="9">
         <v>46313</v>
       </c>
       <c r="P119" s="3" t="s">
@@ -13711,10 +13714,10 @@
       <c r="M120" s="5" t="s">
         <v>2188</v>
       </c>
-      <c r="N120" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O120" s="10">
+      <c r="N120" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O120" s="9">
         <v>46313</v>
       </c>
       <c r="P120" s="3" t="s">
@@ -13761,10 +13764,10 @@
       <c r="M121" s="5" t="s">
         <v>2192</v>
       </c>
-      <c r="N121" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O121" s="10">
+      <c r="N121" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O121" s="9">
         <v>46313</v>
       </c>
       <c r="P121" s="3" t="s">
@@ -13811,10 +13814,10 @@
       <c r="M122" s="5" t="s">
         <v>2195</v>
       </c>
-      <c r="N122" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O122" s="10">
+      <c r="N122" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O122" s="9">
         <v>46313</v>
       </c>
       <c r="P122" s="3" t="s">
@@ -13861,10 +13864,10 @@
       <c r="M123" s="5" t="s">
         <v>2196</v>
       </c>
-      <c r="N123" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O123" s="10">
+      <c r="N123" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O123" s="9">
         <v>46313</v>
       </c>
       <c r="P123" s="3" t="s">
@@ -13911,10 +13914,10 @@
       <c r="M124" s="5" t="s">
         <v>2197</v>
       </c>
-      <c r="N124" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O124" s="10">
+      <c r="N124" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O124" s="9">
         <v>46313</v>
       </c>
       <c r="P124" s="3" t="s">
@@ -13961,17 +13964,17 @@
       <c r="M125" s="5" t="s">
         <v>2188</v>
       </c>
-      <c r="N125" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O125" s="10">
+      <c r="N125" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O125" s="9">
         <v>46313</v>
       </c>
       <c r="P125" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:16" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>167</v>
       </c>
@@ -14011,10 +14014,10 @@
       <c r="M126" s="5" t="s">
         <v>2198</v>
       </c>
-      <c r="N126" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O126" s="10">
+      <c r="N126" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O126" s="9">
         <v>46313</v>
       </c>
       <c r="P126" s="3" t="s">
@@ -14061,10 +14064,10 @@
       <c r="M127" s="5" t="s">
         <v>2199</v>
       </c>
-      <c r="N127" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O127" s="10">
+      <c r="N127" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O127" s="9">
         <v>46313</v>
       </c>
       <c r="P127" s="3" t="s">
@@ -14111,17 +14114,17 @@
       <c r="M128" s="5" t="s">
         <v>2188</v>
       </c>
-      <c r="N128" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O128" s="10">
+      <c r="N128" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O128" s="9">
         <v>46313</v>
       </c>
       <c r="P128" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>167</v>
       </c>
@@ -14161,10 +14164,10 @@
       <c r="M129" s="5" t="s">
         <v>2200</v>
       </c>
-      <c r="N129" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O129" s="10">
+      <c r="N129" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O129" s="9">
         <v>46313</v>
       </c>
       <c r="P129" s="3" t="s">
@@ -14211,10 +14214,10 @@
       <c r="M130" s="5" t="s">
         <v>2201</v>
       </c>
-      <c r="N130" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O130" s="10">
+      <c r="N130" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O130" s="9">
         <v>46313</v>
       </c>
       <c r="P130" s="3" t="s">
@@ -14261,10 +14264,10 @@
       <c r="M131" s="5" t="s">
         <v>2202</v>
       </c>
-      <c r="N131" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O131" s="10">
+      <c r="N131" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O131" s="9">
         <v>46313</v>
       </c>
       <c r="P131" s="3" t="s">
@@ -14311,17 +14314,17 @@
       <c r="M132" s="5" t="s">
         <v>2202</v>
       </c>
-      <c r="N132" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O132" s="10">
+      <c r="N132" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O132" s="9">
         <v>46313</v>
       </c>
       <c r="P132" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>167</v>
       </c>
@@ -14361,17 +14364,17 @@
       <c r="M133" s="5" t="s">
         <v>2202</v>
       </c>
-      <c r="N133" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O133" s="10">
+      <c r="N133" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O133" s="9">
         <v>46313</v>
       </c>
       <c r="P133" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>167</v>
       </c>
@@ -14411,17 +14414,17 @@
       <c r="M134" s="5" t="s">
         <v>2203</v>
       </c>
-      <c r="N134" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O134" s="10">
+      <c r="N134" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O134" s="9">
         <v>46313</v>
       </c>
       <c r="P134" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="144" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>167</v>
       </c>
@@ -14461,10 +14464,10 @@
       <c r="M135" s="5" t="s">
         <v>2203</v>
       </c>
-      <c r="N135" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O135" s="10">
+      <c r="N135" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O135" s="9">
         <v>46313</v>
       </c>
       <c r="P135" s="3" t="s">
@@ -14511,17 +14514,17 @@
       <c r="M136" s="5" t="s">
         <v>2203</v>
       </c>
-      <c r="N136" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O136" s="10">
+      <c r="N136" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O136" s="9">
         <v>46313</v>
       </c>
       <c r="P136" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>47</v>
       </c>
@@ -14561,10 +14564,10 @@
       <c r="M137" s="5" t="s">
         <v>2203</v>
       </c>
-      <c r="N137" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O137" s="10">
+      <c r="N137" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O137" s="9">
         <v>46313</v>
       </c>
       <c r="P137" s="3" t="s">
@@ -14611,17 +14614,17 @@
       <c r="M138" s="5" t="s">
         <v>2203</v>
       </c>
-      <c r="N138" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O138" s="10">
+      <c r="N138" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O138" s="9">
         <v>46313</v>
       </c>
       <c r="P138" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>34</v>
       </c>
@@ -14661,10 +14664,10 @@
       <c r="M139" s="5" t="s">
         <v>2203</v>
       </c>
-      <c r="N139" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O139" s="10">
+      <c r="N139" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O139" s="9">
         <v>46313</v>
       </c>
       <c r="P139" s="3" t="s">
@@ -14711,10 +14714,10 @@
       <c r="M140" s="5" t="s">
         <v>2204</v>
       </c>
-      <c r="N140" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O140" s="10">
+      <c r="N140" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O140" s="9">
         <v>46313</v>
       </c>
       <c r="P140" s="3" t="s">
@@ -14761,17 +14764,17 @@
       <c r="M141" s="5" t="s">
         <v>2204</v>
       </c>
-      <c r="N141" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O141" s="10">
+      <c r="N141" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O141" s="9">
         <v>46313</v>
       </c>
       <c r="P141" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>167</v>
       </c>
@@ -14808,18 +14811,20 @@
       <c r="L142" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M142" s="5"/>
-      <c r="N142" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O142" s="10">
+      <c r="M142" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N142" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O142" s="9">
         <v>46313</v>
       </c>
       <c r="P142" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:16" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>167</v>
       </c>
@@ -14856,18 +14861,20 @@
       <c r="L143" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M143" s="5"/>
-      <c r="N143" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O143" s="10">
+      <c r="M143" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N143" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O143" s="9">
         <v>46313</v>
       </c>
       <c r="P143" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>167</v>
       </c>
@@ -14904,11 +14911,13 @@
       <c r="L144" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M144" s="5"/>
-      <c r="N144" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O144" s="10">
+      <c r="M144" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N144" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O144" s="9">
         <v>46313</v>
       </c>
       <c r="P144" s="3" t="s">
@@ -14952,18 +14961,20 @@
       <c r="L145" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M145" s="5"/>
-      <c r="N145" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O145" s="10">
+      <c r="M145" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N145" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O145" s="9">
         <v>46313</v>
       </c>
       <c r="P145" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:16" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" ht="216" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>167</v>
       </c>
@@ -15000,18 +15011,20 @@
       <c r="L146" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M146" s="5"/>
-      <c r="N146" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O146" s="10">
+      <c r="M146" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N146" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O146" s="9">
         <v>46313</v>
       </c>
       <c r="P146" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:16" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:16" ht="144" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>167</v>
       </c>
@@ -15048,18 +15061,20 @@
       <c r="L147" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M147" s="5"/>
-      <c r="N147" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O147" s="10">
+      <c r="M147" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N147" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O147" s="9">
         <v>46313</v>
       </c>
       <c r="P147" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>167</v>
       </c>
@@ -15096,11 +15111,13 @@
       <c r="L148" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M148" s="5"/>
-      <c r="N148" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O148" s="10">
+      <c r="M148" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N148" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O148" s="9">
         <v>46313</v>
       </c>
       <c r="P148" s="3" t="s">
@@ -15144,18 +15161,20 @@
       <c r="L149" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M149" s="5"/>
-      <c r="N149" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O149" s="10">
+      <c r="M149" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N149" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O149" s="9">
         <v>46313</v>
       </c>
       <c r="P149" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>167</v>
       </c>
@@ -15192,11 +15211,13 @@
       <c r="L150" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M150" s="5"/>
-      <c r="N150" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O150" s="10">
+      <c r="M150" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N150" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O150" s="9">
         <v>46313</v>
       </c>
       <c r="P150" s="3" t="s">
@@ -15240,18 +15261,20 @@
       <c r="L151" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M151" s="5"/>
-      <c r="N151" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O151" s="10">
+      <c r="M151" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N151" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O151" s="9">
         <v>46313</v>
       </c>
       <c r="P151" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="152" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>47</v>
       </c>
@@ -15288,11 +15311,13 @@
       <c r="L152" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M152" s="5"/>
-      <c r="N152" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O152" s="10">
+      <c r="M152" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N152" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O152" s="9">
         <v>46313</v>
       </c>
       <c r="P152" s="3" t="s">
@@ -15336,11 +15361,13 @@
       <c r="L153" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M153" s="5"/>
-      <c r="N153" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O153" s="10">
+      <c r="M153" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N153" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O153" s="9">
         <v>46313</v>
       </c>
       <c r="P153" s="3" t="s">
@@ -15384,18 +15411,20 @@
       <c r="L154" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M154" s="5"/>
-      <c r="N154" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O154" s="10">
+      <c r="M154" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N154" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O154" s="9">
         <v>46313</v>
       </c>
       <c r="P154" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>167</v>
       </c>
@@ -15432,11 +15461,13 @@
       <c r="L155" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M155" s="5"/>
-      <c r="N155" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O155" s="10">
+      <c r="M155" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N155" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O155" s="9">
         <v>46313</v>
       </c>
       <c r="P155" s="3" t="s">
@@ -15480,18 +15511,20 @@
       <c r="L156" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M156" s="5"/>
-      <c r="N156" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O156" s="10">
+      <c r="M156" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N156" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O156" s="9">
         <v>46313</v>
       </c>
       <c r="P156" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="157" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>167</v>
       </c>
@@ -15578,18 +15611,20 @@
       <c r="L158" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M158" s="5"/>
-      <c r="N158" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O158" s="10">
+      <c r="M158" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N158" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O158" s="9">
         <v>46313</v>
       </c>
       <c r="P158" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="159" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>167</v>
       </c>
@@ -15626,11 +15661,13 @@
       <c r="L159" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M159" s="5"/>
-      <c r="N159" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O159" s="10">
+      <c r="M159" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N159" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O159" s="9">
         <v>46313</v>
       </c>
       <c r="P159" s="3" t="s">
@@ -15674,18 +15711,20 @@
       <c r="L160" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M160" s="5"/>
-      <c r="N160" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O160" s="10">
+      <c r="M160" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N160" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O160" s="9">
         <v>46313</v>
       </c>
       <c r="P160" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>47</v>
       </c>
@@ -15722,18 +15761,20 @@
       <c r="L161" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M161" s="5"/>
-      <c r="N161" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O161" s="10">
+      <c r="M161" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="N161" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O161" s="9">
         <v>46313</v>
       </c>
       <c r="P161" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>47</v>
       </c>
@@ -15770,11 +15811,13 @@
       <c r="L162" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M162" s="5"/>
-      <c r="N162" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O162" s="10">
+      <c r="M162" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N162" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O162" s="9">
         <v>46313</v>
       </c>
       <c r="P162" s="3" t="s">
@@ -15818,11 +15861,13 @@
       <c r="L163" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M163" s="5"/>
-      <c r="N163" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O163" s="10">
+      <c r="M163" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N163" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O163" s="9">
         <v>46313</v>
       </c>
       <c r="P163" s="3" t="s">
@@ -15866,18 +15911,20 @@
       <c r="L164" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M164" s="5"/>
-      <c r="N164" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O164" s="10">
+      <c r="M164" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N164" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O164" s="9">
         <v>46313</v>
       </c>
       <c r="P164" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="165" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>34</v>
       </c>
@@ -15914,18 +15961,20 @@
       <c r="L165" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M165" s="5"/>
-      <c r="N165" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O165" s="10">
+      <c r="M165" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N165" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O165" s="9">
         <v>46313</v>
       </c>
       <c r="P165" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="166" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>34</v>
       </c>
@@ -15975,7 +16024,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>167</v>
       </c>
@@ -16012,11 +16061,13 @@
       <c r="L167" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M167" s="5"/>
-      <c r="N167" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O167" s="10">
+      <c r="M167" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N167" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O167" s="9">
         <v>46313</v>
       </c>
       <c r="P167" s="3" t="s">
@@ -16060,11 +16111,13 @@
       <c r="L168" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M168" s="5"/>
-      <c r="N168" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O168" s="10">
+      <c r="M168" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N168" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O168" s="9">
         <v>46313</v>
       </c>
       <c r="P168" s="3" t="s">
@@ -16108,11 +16161,13 @@
       <c r="L169" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M169" s="5"/>
-      <c r="N169" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O169" s="10">
+      <c r="M169" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N169" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O169" s="9">
         <v>46313</v>
       </c>
       <c r="P169" s="3" t="s">
@@ -16156,11 +16211,13 @@
       <c r="L170" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M170" s="5"/>
-      <c r="N170" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O170" s="10">
+      <c r="M170" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N170" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O170" s="9">
         <v>46313</v>
       </c>
       <c r="P170" s="3" t="s">
@@ -16217,7 +16274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>34</v>
       </c>
@@ -16254,11 +16311,13 @@
       <c r="L172" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M172" s="5"/>
-      <c r="N172" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O172" s="10">
+      <c r="M172" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N172" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O172" s="9">
         <v>46313</v>
       </c>
       <c r="P172" s="3" t="s">
@@ -16302,11 +16361,13 @@
       <c r="L173" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M173" s="5"/>
-      <c r="N173" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O173" s="10">
+      <c r="M173" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N173" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O173" s="9">
         <v>46313</v>
       </c>
       <c r="P173" s="3" t="s">
@@ -16350,11 +16411,13 @@
       <c r="L174" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M174" s="5"/>
-      <c r="N174" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O174" s="10">
+      <c r="M174" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N174" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O174" s="9">
         <v>46313</v>
       </c>
       <c r="P174" s="3" t="s">
@@ -16398,11 +16461,13 @@
       <c r="L175" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M175" s="5"/>
-      <c r="N175" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O175" s="10">
+      <c r="M175" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N175" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O175" s="9">
         <v>46313</v>
       </c>
       <c r="P175" s="3" t="s">
@@ -16459,7 +16524,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:16" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>167</v>
       </c>
@@ -16509,7 +16574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>167</v>
       </c>
@@ -16546,18 +16611,20 @@
       <c r="L178" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M178" s="5"/>
-      <c r="N178" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O178" s="10">
+      <c r="M178" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N178" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O178" s="9">
         <v>46313</v>
       </c>
       <c r="P178" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="179" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>167</v>
       </c>
@@ -16594,18 +16661,20 @@
       <c r="L179" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M179" s="5"/>
-      <c r="N179" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O179" s="10">
+      <c r="M179" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N179" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O179" s="9">
         <v>46313</v>
       </c>
       <c r="P179" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="180" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>167</v>
       </c>
@@ -16642,18 +16711,20 @@
       <c r="L180" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M180" s="5"/>
-      <c r="N180" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O180" s="10">
+      <c r="M180" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N180" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O180" s="9">
         <v>46313</v>
       </c>
       <c r="P180" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="181" spans="1:16" ht="216" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:16" ht="288" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>167</v>
       </c>
@@ -16690,18 +16761,20 @@
       <c r="L181" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M181" s="5"/>
-      <c r="N181" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O181" s="10">
+      <c r="M181" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N181" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O181" s="9">
         <v>46313</v>
       </c>
       <c r="P181" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="182" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>167</v>
       </c>
@@ -16738,11 +16811,13 @@
       <c r="L182" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M182" s="5"/>
-      <c r="N182" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O182" s="10">
+      <c r="M182" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N182" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O182" s="9">
         <v>46313</v>
       </c>
       <c r="P182" s="3" t="s">
@@ -16786,11 +16861,13 @@
       <c r="L183" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M183" s="5"/>
-      <c r="N183" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O183" s="10">
+      <c r="M183" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N183" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O183" s="9">
         <v>46313</v>
       </c>
       <c r="P183" s="3" t="s">
@@ -16834,11 +16911,13 @@
       <c r="L184" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M184" s="5"/>
-      <c r="N184" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O184" s="10">
+      <c r="M184" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N184" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O184" s="9">
         <v>46313</v>
       </c>
       <c r="P184" s="3" t="s">
@@ -16882,18 +16961,20 @@
       <c r="L185" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M185" s="5"/>
-      <c r="N185" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O185" s="10">
+      <c r="M185" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N185" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O185" s="9">
         <v>46313</v>
       </c>
       <c r="P185" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="186" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:16" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>167</v>
       </c>
@@ -16930,18 +17011,20 @@
       <c r="L186" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M186" s="5"/>
-      <c r="N186" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O186" s="10">
+      <c r="M186" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N186" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O186" s="9">
         <v>46313</v>
       </c>
       <c r="P186" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="187" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>167</v>
       </c>
@@ -16978,18 +17061,20 @@
       <c r="L187" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M187" s="5"/>
-      <c r="N187" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O187" s="10">
+      <c r="M187" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N187" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O187" s="9">
         <v>46313</v>
       </c>
       <c r="P187" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>167</v>
       </c>
@@ -17026,18 +17111,20 @@
       <c r="L188" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M188" s="5"/>
-      <c r="N188" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O188" s="10">
+      <c r="M188" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N188" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O188" s="9">
         <v>46313</v>
       </c>
       <c r="P188" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="189" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>167</v>
       </c>
@@ -17074,18 +17161,20 @@
       <c r="L189" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M189" s="5"/>
-      <c r="N189" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O189" s="10">
+      <c r="M189" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N189" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O189" s="9">
         <v>46313</v>
       </c>
       <c r="P189" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>167</v>
       </c>
@@ -17122,18 +17211,20 @@
       <c r="L190" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M190" s="5"/>
-      <c r="N190" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O190" s="10">
+      <c r="M190" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N190" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O190" s="9">
         <v>46313</v>
       </c>
       <c r="P190" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="191" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:16" ht="144" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>167</v>
       </c>
@@ -17170,18 +17261,20 @@
       <c r="L191" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M191" s="5"/>
-      <c r="N191" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O191" s="10">
+      <c r="M191" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N191" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O191" s="9">
         <v>46313</v>
       </c>
       <c r="P191" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="192" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>167</v>
       </c>
@@ -17218,18 +17311,20 @@
       <c r="L192" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M192" s="5"/>
-      <c r="N192" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O192" s="10">
+      <c r="M192" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N192" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O192" s="9">
         <v>46313</v>
       </c>
       <c r="P192" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="193" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:16" ht="216" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>167</v>
       </c>
@@ -17266,18 +17361,20 @@
       <c r="L193" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M193" s="5"/>
-      <c r="N193" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O193" s="10">
+      <c r="M193" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N193" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O193" s="9">
         <v>46313</v>
       </c>
       <c r="P193" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="194" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>167</v>
       </c>
@@ -17327,7 +17424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:16" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:16" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>167</v>
       </c>
@@ -17364,18 +17461,20 @@
       <c r="L195" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M195" s="5"/>
-      <c r="N195" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O195" s="10">
+      <c r="M195" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N195" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O195" s="9">
         <v>46313</v>
       </c>
       <c r="P195" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="196" spans="1:16" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:16" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>167</v>
       </c>
@@ -17412,18 +17511,20 @@
       <c r="L196" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M196" s="5"/>
-      <c r="N196" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O196" s="10">
+      <c r="M196" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N196" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O196" s="9">
         <v>46313</v>
       </c>
       <c r="P196" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="197" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>167</v>
       </c>
@@ -17460,11 +17561,13 @@
       <c r="L197" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M197" s="5"/>
-      <c r="N197" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O197" s="10">
+      <c r="M197" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N197" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O197" s="9">
         <v>46313</v>
       </c>
       <c r="P197" s="3" t="s">
@@ -17508,11 +17611,13 @@
       <c r="L198" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M198" s="5"/>
-      <c r="N198" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O198" s="10">
+      <c r="M198" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N198" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O198" s="9">
         <v>46313</v>
       </c>
       <c r="P198" s="3" t="s">
@@ -17556,11 +17661,13 @@
       <c r="L199" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M199" s="5"/>
-      <c r="N199" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O199" s="10">
+      <c r="M199" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N199" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O199" s="9">
         <v>46313</v>
       </c>
       <c r="P199" s="3" t="s">
@@ -17604,11 +17711,13 @@
       <c r="L200" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M200" s="5"/>
-      <c r="N200" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O200" s="10">
+      <c r="M200" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N200" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O200" s="9">
         <v>46313</v>
       </c>
       <c r="P200" s="3" t="s">
@@ -17702,11 +17811,13 @@
       <c r="L202" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M202" s="5"/>
-      <c r="N202" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O202" s="10">
+      <c r="M202" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N202" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O202" s="9">
         <v>46313</v>
       </c>
       <c r="P202" s="3" t="s">
@@ -17750,18 +17861,20 @@
       <c r="L203" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M203" s="5"/>
-      <c r="N203" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O203" s="10">
+      <c r="M203" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N203" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O203" s="9">
         <v>46313</v>
       </c>
       <c r="P203" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="204" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>47</v>
       </c>
@@ -17798,18 +17911,20 @@
       <c r="L204" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M204" s="5"/>
-      <c r="N204" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O204" s="10">
+      <c r="M204" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N204" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O204" s="9">
         <v>46313</v>
       </c>
       <c r="P204" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="205" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>167</v>
       </c>
@@ -17846,11 +17961,13 @@
       <c r="L205" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M205" s="5"/>
-      <c r="N205" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O205" s="10">
+      <c r="M205" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="N205" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O205" s="9">
         <v>46313</v>
       </c>
       <c r="P205" s="3" t="s">
@@ -17894,18 +18011,20 @@
       <c r="L206" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M206" s="5"/>
-      <c r="N206" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O206" s="10">
+      <c r="M206" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N206" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O206" s="9">
         <v>46313</v>
       </c>
       <c r="P206" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="207" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>167</v>
       </c>
@@ -17942,18 +18061,20 @@
       <c r="L207" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M207" s="5"/>
-      <c r="N207" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O207" s="10">
+      <c r="M207" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N207" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O207" s="9">
         <v>46313</v>
       </c>
       <c r="P207" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="208" spans="1:16" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:16" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>167</v>
       </c>
@@ -17990,11 +18111,13 @@
       <c r="L208" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M208" s="5"/>
-      <c r="N208" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O208" s="10">
+      <c r="M208" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N208" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O208" s="9">
         <v>46313</v>
       </c>
       <c r="P208" s="3" t="s">
@@ -18038,11 +18161,13 @@
       <c r="L209" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M209" s="5"/>
-      <c r="N209" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O209" s="10">
+      <c r="M209" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N209" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O209" s="9">
         <v>46313</v>
       </c>
       <c r="P209" s="3" t="s">
@@ -18086,18 +18211,20 @@
       <c r="L210" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M210" s="5"/>
-      <c r="N210" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O210" s="10">
+      <c r="M210" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N210" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O210" s="9">
         <v>46313</v>
       </c>
       <c r="P210" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="211" spans="1:16" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:16" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>167</v>
       </c>
@@ -18134,18 +18261,20 @@
       <c r="L211" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M211" s="5"/>
-      <c r="N211" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O211" s="10">
+      <c r="M211" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N211" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O211" s="9">
         <v>46313</v>
       </c>
       <c r="P211" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="212" spans="1:16" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:16" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>167</v>
       </c>
@@ -18182,18 +18311,20 @@
       <c r="L212" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M212" s="5"/>
-      <c r="N212" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O212" s="10">
+      <c r="M212" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N212" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O212" s="9">
         <v>46313</v>
       </c>
       <c r="P212" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="213" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>167</v>
       </c>
@@ -18230,11 +18361,13 @@
       <c r="L213" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M213" s="5"/>
-      <c r="N213" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O213" s="10">
+      <c r="M213" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N213" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O213" s="9">
         <v>46313</v>
       </c>
       <c r="P213" s="3" t="s">
@@ -18278,11 +18411,13 @@
       <c r="L214" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M214" s="5"/>
-      <c r="N214" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O214" s="10">
+      <c r="M214" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N214" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O214" s="9">
         <v>46313</v>
       </c>
       <c r="P214" s="3" t="s">
@@ -18376,11 +18511,13 @@
       <c r="L216" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M216" s="5"/>
-      <c r="N216" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O216" s="10">
+      <c r="M216" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N216" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O216" s="9">
         <v>46313</v>
       </c>
       <c r="P216" s="3" t="s">
@@ -18424,18 +18561,20 @@
       <c r="L217" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M217" s="5"/>
-      <c r="N217" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O217" s="10">
+      <c r="M217" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N217" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O217" s="9">
         <v>46313</v>
       </c>
       <c r="P217" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>34</v>
       </c>
@@ -18472,11 +18611,13 @@
       <c r="L218" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M218" s="5"/>
-      <c r="N218" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O218" s="10">
+      <c r="M218" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N218" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O218" s="9">
         <v>46313</v>
       </c>
       <c r="P218" s="3" t="s">
@@ -18520,11 +18661,13 @@
       <c r="L219" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M219" s="5"/>
-      <c r="N219" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O219" s="10">
+      <c r="M219" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N219" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O219" s="9">
         <v>46313</v>
       </c>
       <c r="P219" s="3" t="s">
@@ -18568,11 +18711,13 @@
       <c r="L220" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M220" s="5"/>
-      <c r="N220" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O220" s="10">
+      <c r="M220" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N220" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O220" s="9">
         <v>46313</v>
       </c>
       <c r="P220" s="3" t="s">
@@ -18616,11 +18761,13 @@
       <c r="L221" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M221" s="5"/>
-      <c r="N221" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O221" s="10">
+      <c r="M221" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N221" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O221" s="9">
         <v>46313</v>
       </c>
       <c r="P221" s="3" t="s">
@@ -18664,11 +18811,13 @@
       <c r="L222" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M222" s="5"/>
-      <c r="N222" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O222" s="10">
+      <c r="M222" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N222" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O222" s="9">
         <v>46313</v>
       </c>
       <c r="P222" s="3" t="s">
@@ -18712,11 +18861,13 @@
       <c r="L223" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M223" s="5"/>
-      <c r="N223" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O223" s="10">
+      <c r="M223" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N223" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O223" s="9">
         <v>46313</v>
       </c>
       <c r="P223" s="3" t="s">
@@ -18760,11 +18911,13 @@
       <c r="L224" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M224" s="5"/>
-      <c r="N224" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O224" s="10">
+      <c r="M224" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N224" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O224" s="9">
         <v>46313</v>
       </c>
       <c r="P224" s="3" t="s">
@@ -18808,11 +18961,13 @@
       <c r="L225" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M225" s="5"/>
-      <c r="N225" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O225" s="10">
+      <c r="M225" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N225" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O225" s="9">
         <v>46313</v>
       </c>
       <c r="P225" s="3" t="s">
@@ -18856,11 +19011,13 @@
       <c r="L226" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M226" s="5"/>
-      <c r="N226" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O226" s="10">
+      <c r="M226" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N226" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O226" s="9">
         <v>46313</v>
       </c>
       <c r="P226" s="3" t="s">
@@ -18904,11 +19061,13 @@
       <c r="L227" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M227" s="5"/>
-      <c r="N227" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O227" s="10">
+      <c r="M227" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N227" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O227" s="9">
         <v>46313</v>
       </c>
       <c r="P227" s="3" t="s">
@@ -18952,11 +19111,13 @@
       <c r="L228" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M228" s="5"/>
-      <c r="N228" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O228" s="10">
+      <c r="M228" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N228" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O228" s="9">
         <v>46313</v>
       </c>
       <c r="P228" s="3" t="s">
@@ -19063,7 +19224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>34</v>
       </c>
@@ -19100,11 +19261,13 @@
       <c r="L231" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M231" s="5"/>
-      <c r="N231" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O231" s="10">
+      <c r="M231" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N231" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O231" s="9">
         <v>46313</v>
       </c>
       <c r="P231" s="3" t="s">
@@ -19148,11 +19311,13 @@
       <c r="L232" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M232" s="5"/>
-      <c r="N232" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O232" s="10">
+      <c r="M232" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N232" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O232" s="9">
         <v>46313</v>
       </c>
       <c r="P232" s="3" t="s">
@@ -19209,7 +19374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="234" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>47</v>
       </c>
@@ -19259,7 +19424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>47</v>
       </c>
@@ -19296,18 +19461,20 @@
       <c r="L235" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M235" s="5"/>
-      <c r="N235" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O235" s="10">
+      <c r="M235" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N235" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O235" s="9">
         <v>46313</v>
       </c>
       <c r="P235" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>47</v>
       </c>
@@ -19344,11 +19511,13 @@
       <c r="L236" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M236" s="5"/>
-      <c r="N236" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O236" s="10">
+      <c r="M236" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N236" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O236" s="9">
         <v>46313</v>
       </c>
       <c r="P236" s="3" t="s">
@@ -19392,11 +19561,13 @@
       <c r="L237" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M237" s="5"/>
-      <c r="N237" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O237" s="10">
+      <c r="M237" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N237" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O237" s="9">
         <v>46313</v>
       </c>
       <c r="P237" s="3" t="s">
@@ -19440,18 +19611,20 @@
       <c r="L238" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M238" s="5"/>
-      <c r="N238" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O238" s="10">
+      <c r="M238" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N238" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O238" s="9">
         <v>46313</v>
       </c>
       <c r="P238" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>47</v>
       </c>
@@ -19488,18 +19661,20 @@
       <c r="L239" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M239" s="5"/>
-      <c r="N239" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O239" s="10">
+      <c r="M239" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N239" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O239" s="9">
         <v>46313</v>
       </c>
       <c r="P239" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>47</v>
       </c>
@@ -19536,18 +19711,20 @@
       <c r="L240" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M240" s="5"/>
-      <c r="N240" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O240" s="10">
+      <c r="M240" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N240" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O240" s="9">
         <v>46313</v>
       </c>
       <c r="P240" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>47</v>
       </c>
@@ -19584,18 +19761,20 @@
       <c r="L241" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M241" s="5"/>
-      <c r="N241" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O241" s="10">
+      <c r="M241" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N241" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O241" s="9">
         <v>46313</v>
       </c>
       <c r="P241" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="242" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>47</v>
       </c>
@@ -19632,18 +19811,20 @@
       <c r="L242" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M242" s="5"/>
-      <c r="N242" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O242" s="10">
+      <c r="M242" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N242" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O242" s="9">
         <v>46313</v>
       </c>
       <c r="P242" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>47</v>
       </c>
@@ -19680,18 +19861,20 @@
       <c r="L243" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M243" s="5"/>
-      <c r="N243" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O243" s="10">
+      <c r="M243" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N243" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O243" s="9">
         <v>46313</v>
       </c>
       <c r="P243" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="244" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
         <v>34</v>
       </c>
@@ -19728,11 +19911,13 @@
       <c r="L244" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M244" s="5"/>
-      <c r="N244" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O244" s="10">
+      <c r="M244" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N244" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O244" s="9">
         <v>46313</v>
       </c>
       <c r="P244" s="3" t="s">
@@ -19776,11 +19961,13 @@
       <c r="L245" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M245" s="5"/>
-      <c r="N245" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O245" s="10">
+      <c r="M245" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N245" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O245" s="9">
         <v>46313</v>
       </c>
       <c r="P245" s="3" t="s">
@@ -19824,11 +20011,13 @@
       <c r="L246" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M246" s="5"/>
-      <c r="N246" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O246" s="10">
+      <c r="M246" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N246" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O246" s="9">
         <v>46313</v>
       </c>
       <c r="P246" s="3" t="s">
@@ -19872,11 +20061,13 @@
       <c r="L247" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M247" s="5"/>
-      <c r="N247" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O247" s="10">
+      <c r="M247" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N247" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O247" s="9">
         <v>46313</v>
       </c>
       <c r="P247" s="3" t="s">
@@ -19920,11 +20111,13 @@
       <c r="L248" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M248" s="5"/>
-      <c r="N248" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O248" s="10">
+      <c r="M248" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N248" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O248" s="9">
         <v>46313</v>
       </c>
       <c r="P248" s="3" t="s">
@@ -19968,11 +20161,13 @@
       <c r="L249" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M249" s="5"/>
-      <c r="N249" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O249" s="10">
+      <c r="M249" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N249" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O249" s="9">
         <v>46313</v>
       </c>
       <c r="P249" s="3" t="s">
@@ -20016,18 +20211,20 @@
       <c r="L250" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M250" s="5"/>
-      <c r="N250" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O250" s="10">
+      <c r="M250" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N250" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O250" s="9">
         <v>46313</v>
       </c>
       <c r="P250" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="251" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
         <v>34</v>
       </c>
@@ -20064,11 +20261,13 @@
       <c r="L251" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M251" s="5"/>
-      <c r="N251" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O251" s="10">
+      <c r="M251" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N251" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O251" s="9">
         <v>46313</v>
       </c>
       <c r="P251" s="3" t="s">
@@ -20112,11 +20311,13 @@
       <c r="L252" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M252" s="5"/>
-      <c r="N252" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O252" s="10">
+      <c r="M252" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N252" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O252" s="9">
         <v>46313</v>
       </c>
       <c r="P252" s="3" t="s">
@@ -20160,11 +20361,13 @@
       <c r="L253" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M253" s="5"/>
-      <c r="N253" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O253" s="10">
+      <c r="M253" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N253" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O253" s="9">
         <v>46313</v>
       </c>
       <c r="P253" s="3" t="s">
@@ -20208,18 +20411,20 @@
       <c r="L254" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M254" s="5"/>
-      <c r="N254" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O254" s="10">
+      <c r="M254" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N254" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O254" s="9">
         <v>46313</v>
       </c>
       <c r="P254" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="255" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
         <v>34</v>
       </c>
@@ -20256,11 +20461,13 @@
       <c r="L255" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M255" s="5"/>
-      <c r="N255" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O255" s="10">
+      <c r="M255" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N255" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O255" s="9">
         <v>46313</v>
       </c>
       <c r="P255" s="3" t="s">
@@ -20304,18 +20511,20 @@
       <c r="L256" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M256" s="5"/>
-      <c r="N256" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O256" s="10">
+      <c r="M256" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N256" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O256" s="9">
         <v>46313</v>
       </c>
       <c r="P256" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="257" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
         <v>34</v>
       </c>
@@ -20352,18 +20561,20 @@
       <c r="L257" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M257" s="5"/>
-      <c r="N257" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O257" s="10">
+      <c r="M257" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="N257" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O257" s="9">
         <v>46313</v>
       </c>
       <c r="P257" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="258" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
         <v>34</v>
       </c>
@@ -20400,18 +20611,20 @@
       <c r="L258" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M258" s="5"/>
-      <c r="N258" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O258" s="10">
+      <c r="M258" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N258" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O258" s="9">
         <v>46313</v>
       </c>
       <c r="P258" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
         <v>34</v>
       </c>
@@ -20448,11 +20661,13 @@
       <c r="L259" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M259" s="5"/>
-      <c r="N259" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O259" s="10">
+      <c r="M259" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="N259" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O259" s="9">
         <v>46313</v>
       </c>
       <c r="P259" s="3" t="s">
@@ -20496,11 +20711,13 @@
       <c r="L260" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M260" s="5"/>
-      <c r="N260" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O260" s="10">
+      <c r="M260" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N260" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O260" s="9">
         <v>46313</v>
       </c>
       <c r="P260" s="3" t="s">
@@ -20544,18 +20761,20 @@
       <c r="L261" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M261" s="5"/>
-      <c r="N261" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O261" s="10">
+      <c r="M261" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N261" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O261" s="9">
         <v>46313</v>
       </c>
       <c r="P261" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="262" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
         <v>47</v>
       </c>
@@ -20592,11 +20811,13 @@
       <c r="L262" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M262" s="5"/>
-      <c r="N262" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O262" s="10">
+      <c r="M262" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N262" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O262" s="9">
         <v>46313</v>
       </c>
       <c r="P262" s="3" t="s">
@@ -20640,11 +20861,13 @@
       <c r="L263" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M263" s="5"/>
-      <c r="N263" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O263" s="10">
+      <c r="M263" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N263" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O263" s="9">
         <v>46313</v>
       </c>
       <c r="P263" s="3" t="s">
@@ -20688,11 +20911,13 @@
       <c r="L264" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M264" s="5"/>
-      <c r="N264" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O264" s="10">
+      <c r="M264" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N264" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O264" s="9">
         <v>46313</v>
       </c>
       <c r="P264" s="3" t="s">
@@ -20736,18 +20961,20 @@
       <c r="L265" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M265" s="5"/>
-      <c r="N265" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O265" s="10">
+      <c r="M265" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N265" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O265" s="9">
         <v>46313</v>
       </c>
       <c r="P265" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="266" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
         <v>34</v>
       </c>
@@ -20784,18 +21011,20 @@
       <c r="L266" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M266" s="5"/>
-      <c r="N266" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O266" s="10">
+      <c r="M266" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N266" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O266" s="9">
         <v>46313</v>
       </c>
       <c r="P266" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="267" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
         <v>34</v>
       </c>
@@ -20832,18 +21061,20 @@
       <c r="L267" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M267" s="5"/>
-      <c r="N267" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O267" s="10">
+      <c r="M267" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N267" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O267" s="9">
         <v>46313</v>
       </c>
       <c r="P267" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="268" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
         <v>34</v>
       </c>
@@ -20880,18 +21111,20 @@
       <c r="L268" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M268" s="5"/>
-      <c r="N268" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O268" s="10">
+      <c r="M268" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N268" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O268" s="9">
         <v>46313</v>
       </c>
       <c r="P268" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="269" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
         <v>34</v>
       </c>
@@ -20928,18 +21161,20 @@
       <c r="L269" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M269" s="5"/>
-      <c r="N269" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O269" s="10">
+      <c r="M269" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N269" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O269" s="9">
         <v>46313</v>
       </c>
       <c r="P269" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="270" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
         <v>34</v>
       </c>
@@ -20976,11 +21211,13 @@
       <c r="L270" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M270" s="5"/>
-      <c r="N270" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O270" s="10">
+      <c r="M270" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N270" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O270" s="9">
         <v>46313</v>
       </c>
       <c r="P270" s="3" t="s">
@@ -21024,18 +21261,20 @@
       <c r="L271" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M271" s="5"/>
-      <c r="N271" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O271" s="10">
+      <c r="M271" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N271" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O271" s="9">
         <v>46313</v>
       </c>
       <c r="P271" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="272" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
         <v>34</v>
       </c>
@@ -21072,11 +21311,13 @@
       <c r="L272" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M272" s="5"/>
-      <c r="N272" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O272" s="10">
+      <c r="M272" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N272" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O272" s="9">
         <v>46313</v>
       </c>
       <c r="P272" s="3" t="s">
@@ -21120,18 +21361,20 @@
       <c r="L273" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M273" s="5"/>
-      <c r="N273" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O273" s="10">
+      <c r="M273" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N273" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O273" s="9">
         <v>46313</v>
       </c>
       <c r="P273" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
         <v>34</v>
       </c>
@@ -21168,11 +21411,13 @@
       <c r="L274" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M274" s="5"/>
-      <c r="N274" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O274" s="10">
+      <c r="M274" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N274" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O274" s="9">
         <v>46313</v>
       </c>
       <c r="P274" s="3" t="s">
@@ -21229,7 +21474,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="276" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
         <v>34</v>
       </c>
@@ -21266,18 +21511,20 @@
       <c r="L276" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M276" s="5"/>
-      <c r="N276" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O276" s="10">
+      <c r="M276" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N276" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O276" s="9">
         <v>46313</v>
       </c>
       <c r="P276" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>47</v>
       </c>
@@ -21364,11 +21611,13 @@
       <c r="L278" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M278" s="5"/>
-      <c r="N278" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O278" s="10">
+      <c r="M278" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N278" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O278" s="9">
         <v>46313</v>
       </c>
       <c r="P278" s="3" t="s">
@@ -21412,11 +21661,13 @@
       <c r="L279" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M279" s="5"/>
-      <c r="N279" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O279" s="10">
+      <c r="M279" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N279" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O279" s="9">
         <v>46313</v>
       </c>
       <c r="P279" s="3" t="s">
@@ -21460,18 +21711,20 @@
       <c r="L280" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M280" s="5"/>
-      <c r="N280" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O280" s="10">
+      <c r="M280" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N280" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O280" s="9">
         <v>46313</v>
       </c>
       <c r="P280" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
         <v>47</v>
       </c>
@@ -21508,18 +21761,20 @@
       <c r="L281" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M281" s="5"/>
-      <c r="N281" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O281" s="10">
+      <c r="M281" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N281" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O281" s="9">
         <v>46313</v>
       </c>
       <c r="P281" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="282" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
         <v>34</v>
       </c>
@@ -21556,18 +21811,20 @@
       <c r="L282" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M282" s="5"/>
-      <c r="N282" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O282" s="10">
+      <c r="M282" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N282" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O282" s="9">
         <v>46313</v>
       </c>
       <c r="P282" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="283" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
         <v>34</v>
       </c>
@@ -21604,18 +21861,20 @@
       <c r="L283" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M283" s="5"/>
-      <c r="N283" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O283" s="10">
+      <c r="M283" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N283" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O283" s="9">
         <v>46313</v>
       </c>
       <c r="P283" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="284" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
         <v>47</v>
       </c>
@@ -21652,11 +21911,13 @@
       <c r="L284" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M284" s="5"/>
-      <c r="N284" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O284" s="10">
+      <c r="M284" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N284" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O284" s="9">
         <v>46313</v>
       </c>
       <c r="P284" s="3" t="s">
@@ -21700,18 +21961,20 @@
       <c r="L285" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M285" s="5"/>
-      <c r="N285" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O285" s="10">
+      <c r="M285" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N285" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O285" s="9">
         <v>46313</v>
       </c>
       <c r="P285" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="286" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
         <v>47</v>
       </c>
@@ -21748,11 +22011,13 @@
       <c r="L286" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M286" s="5"/>
-      <c r="N286" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O286" s="10">
+      <c r="M286" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N286" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O286" s="9">
         <v>46313</v>
       </c>
       <c r="P286" s="3" t="s">
@@ -21796,11 +22061,13 @@
       <c r="L287" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M287" s="5"/>
-      <c r="N287" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O287" s="10">
+      <c r="M287" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N287" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O287" s="9">
         <v>46313</v>
       </c>
       <c r="P287" s="3" t="s">
@@ -21844,18 +22111,20 @@
       <c r="L288" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M288" s="5"/>
-      <c r="N288" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O288" s="10">
+      <c r="M288" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N288" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O288" s="9">
         <v>46313</v>
       </c>
       <c r="P288" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
         <v>47</v>
       </c>
@@ -21892,11 +22161,13 @@
       <c r="L289" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M289" s="5"/>
-      <c r="N289" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O289" s="10">
+      <c r="M289" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N289" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O289" s="9">
         <v>46313</v>
       </c>
       <c r="P289" s="3" t="s">
@@ -21953,7 +22224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>47</v>
       </c>
@@ -22003,7 +22274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A292" s="3" t="s">
         <v>47</v>
       </c>
@@ -22040,18 +22311,20 @@
       <c r="L292" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M292" s="5"/>
-      <c r="N292" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O292" s="10">
+      <c r="M292" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N292" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O292" s="9">
         <v>46313</v>
       </c>
       <c r="P292" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="293" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
         <v>47</v>
       </c>
@@ -22088,11 +22361,13 @@
       <c r="L293" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M293" s="5"/>
-      <c r="N293" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O293" s="10">
+      <c r="M293" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N293" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O293" s="9">
         <v>46313</v>
       </c>
       <c r="P293" s="3" t="s">
@@ -22136,18 +22411,20 @@
       <c r="L294" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M294" s="5"/>
-      <c r="N294" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O294" s="10">
+      <c r="M294" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N294" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O294" s="9">
         <v>46313</v>
       </c>
       <c r="P294" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="295" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
         <v>47</v>
       </c>
@@ -22184,18 +22461,20 @@
       <c r="L295" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M295" s="5"/>
-      <c r="N295" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O295" s="10">
+      <c r="M295" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N295" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O295" s="9">
         <v>46313</v>
       </c>
       <c r="P295" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="296" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A296" s="3" t="s">
         <v>47</v>
       </c>
@@ -22232,18 +22511,20 @@
       <c r="L296" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M296" s="5"/>
-      <c r="N296" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O296" s="10">
+      <c r="M296" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N296" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O296" s="9">
         <v>46313</v>
       </c>
       <c r="P296" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
         <v>47</v>
       </c>
@@ -22280,18 +22561,20 @@
       <c r="L297" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M297" s="5"/>
-      <c r="N297" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O297" s="10">
+      <c r="M297" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N297" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O297" s="9">
         <v>46313</v>
       </c>
       <c r="P297" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A298" s="3" t="s">
         <v>47</v>
       </c>
@@ -22328,11 +22611,13 @@
       <c r="L298" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M298" s="5"/>
-      <c r="N298" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O298" s="10">
+      <c r="M298" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N298" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O298" s="9">
         <v>46313</v>
       </c>
       <c r="P298" s="3" t="s">
@@ -22376,11 +22661,13 @@
       <c r="L299" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M299" s="5"/>
-      <c r="N299" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O299" s="10">
+      <c r="M299" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N299" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O299" s="9">
         <v>46313</v>
       </c>
       <c r="P299" s="3" t="s">
@@ -22424,18 +22711,20 @@
       <c r="L300" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M300" s="5"/>
-      <c r="N300" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O300" s="10">
+      <c r="M300" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N300" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O300" s="9">
         <v>46313</v>
       </c>
       <c r="P300" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
         <v>34</v>
       </c>
@@ -22472,18 +22761,20 @@
       <c r="L301" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M301" s="5"/>
-      <c r="N301" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O301" s="10">
+      <c r="M301" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N301" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O301" s="9">
         <v>46313</v>
       </c>
       <c r="P301" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
         <v>34</v>
       </c>
@@ -22520,11 +22811,13 @@
       <c r="L302" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M302" s="5"/>
-      <c r="N302" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O302" s="10">
+      <c r="M302" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N302" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O302" s="9">
         <v>46313</v>
       </c>
       <c r="P302" s="3" t="s">
@@ -22568,18 +22861,20 @@
       <c r="L303" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M303" s="5"/>
-      <c r="N303" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O303" s="10">
+      <c r="M303" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N303" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O303" s="9">
         <v>46313</v>
       </c>
       <c r="P303" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="304" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A304" s="3" t="s">
         <v>47</v>
       </c>
@@ -22616,11 +22911,13 @@
       <c r="L304" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M304" s="5"/>
-      <c r="N304" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O304" s="10">
+      <c r="M304" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N304" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O304" s="9">
         <v>46313</v>
       </c>
       <c r="P304" s="3" t="s">
@@ -22664,11 +22961,13 @@
       <c r="L305" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M305" s="5"/>
-      <c r="N305" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O305" s="10">
+      <c r="M305" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N305" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O305" s="9">
         <v>46313</v>
       </c>
       <c r="P305" s="3" t="s">
@@ -22712,18 +23011,20 @@
       <c r="L306" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M306" s="5"/>
-      <c r="N306" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O306" s="10">
+      <c r="M306" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N306" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O306" s="9">
         <v>46313</v>
       </c>
       <c r="P306" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
         <v>47</v>
       </c>
@@ -22760,11 +23061,13 @@
       <c r="L307" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M307" s="5"/>
-      <c r="N307" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O307" s="10">
+      <c r="M307" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N307" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O307" s="9">
         <v>46313</v>
       </c>
       <c r="P307" s="3" t="s">
@@ -22808,18 +23111,20 @@
       <c r="L308" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M308" s="5"/>
-      <c r="N308" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O308" s="10">
+      <c r="M308" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N308" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O308" s="9">
         <v>46313</v>
       </c>
       <c r="P308" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="309" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
         <v>47</v>
       </c>
@@ -22856,18 +23161,20 @@
       <c r="L309" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M309" s="5"/>
-      <c r="N309" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O309" s="10">
+      <c r="M309" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N309" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O309" s="9">
         <v>46313</v>
       </c>
       <c r="P309" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="310" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A310" s="3" t="s">
         <v>47</v>
       </c>
@@ -22904,11 +23211,13 @@
       <c r="L310" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M310" s="5"/>
-      <c r="N310" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O310" s="10">
+      <c r="M310" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N310" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O310" s="9">
         <v>46313</v>
       </c>
       <c r="P310" s="3" t="s">
@@ -22952,11 +23261,13 @@
       <c r="L311" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M311" s="5"/>
-      <c r="N311" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O311" s="10">
+      <c r="M311" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N311" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O311" s="9">
         <v>46313</v>
       </c>
       <c r="P311" s="3" t="s">
@@ -23000,11 +23311,13 @@
       <c r="L312" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M312" s="5"/>
-      <c r="N312" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O312" s="10">
+      <c r="M312" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N312" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O312" s="9">
         <v>46313</v>
       </c>
       <c r="P312" s="3" t="s">
@@ -23061,7 +23374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
         <v>47</v>
       </c>
@@ -23098,18 +23411,20 @@
       <c r="L314" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M314" s="5"/>
-      <c r="N314" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O314" s="10">
+      <c r="M314" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N314" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O314" s="9">
         <v>46313</v>
       </c>
       <c r="P314" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="315" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
         <v>47</v>
       </c>
@@ -23146,11 +23461,13 @@
       <c r="L315" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M315" s="5"/>
-      <c r="N315" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O315" s="10">
+      <c r="M315" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N315" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O315" s="9">
         <v>46313</v>
       </c>
       <c r="P315" s="3" t="s">
@@ -23194,11 +23511,13 @@
       <c r="L316" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M316" s="5"/>
-      <c r="N316" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O316" s="10">
+      <c r="M316" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N316" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O316" s="9">
         <v>46313</v>
       </c>
       <c r="P316" s="3" t="s">
@@ -23242,11 +23561,13 @@
       <c r="L317" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M317" s="5"/>
-      <c r="N317" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O317" s="10">
+      <c r="M317" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N317" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O317" s="9">
         <v>46313</v>
       </c>
       <c r="P317" s="3" t="s">
@@ -23290,11 +23611,13 @@
       <c r="L318" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M318" s="5"/>
-      <c r="N318" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O318" s="10">
+      <c r="M318" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N318" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O318" s="9">
         <v>46313</v>
       </c>
       <c r="P318" s="3" t="s">
@@ -23338,11 +23661,13 @@
       <c r="L319" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M319" s="5"/>
-      <c r="N319" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O319" s="10">
+      <c r="M319" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N319" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O319" s="9">
         <v>46313</v>
       </c>
       <c r="P319" s="3" t="s">
@@ -23386,11 +23711,13 @@
       <c r="L320" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M320" s="5"/>
-      <c r="N320" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O320" s="10">
+      <c r="M320" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N320" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O320" s="9">
         <v>46313</v>
       </c>
       <c r="P320" s="3" t="s">
@@ -23434,18 +23761,20 @@
       <c r="L321" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M321" s="5"/>
-      <c r="N321" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O321" s="10">
+      <c r="M321" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N321" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O321" s="9">
         <v>46313</v>
       </c>
       <c r="P321" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
         <v>47</v>
       </c>
@@ -23482,11 +23811,13 @@
       <c r="L322" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M322" s="5"/>
-      <c r="N322" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O322" s="10">
+      <c r="M322" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N322" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O322" s="9">
         <v>46313</v>
       </c>
       <c r="P322" s="3" t="s">
@@ -23530,18 +23861,20 @@
       <c r="L323" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M323" s="5"/>
-      <c r="N323" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O323" s="10">
+      <c r="M323" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N323" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O323" s="9">
         <v>46313</v>
       </c>
       <c r="P323" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A324" s="3" t="s">
         <v>47</v>
       </c>
@@ -23578,11 +23911,13 @@
       <c r="L324" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M324" s="5"/>
-      <c r="N324" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O324" s="10">
+      <c r="M324" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N324" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O324" s="9">
         <v>46313</v>
       </c>
       <c r="P324" s="3" t="s">
@@ -23626,11 +23961,13 @@
       <c r="L325" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M325" s="5"/>
-      <c r="N325" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O325" s="10">
+      <c r="M325" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N325" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O325" s="9">
         <v>46313</v>
       </c>
       <c r="P325" s="3" t="s">
@@ -23674,18 +24011,20 @@
       <c r="L326" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M326" s="5"/>
-      <c r="N326" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O326" s="10">
+      <c r="M326" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N326" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O326" s="9">
         <v>46313</v>
       </c>
       <c r="P326" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
         <v>47</v>
       </c>
@@ -23722,11 +24061,13 @@
       <c r="L327" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M327" s="5"/>
-      <c r="N327" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O327" s="10">
+      <c r="M327" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N327" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O327" s="9">
         <v>46313</v>
       </c>
       <c r="P327" s="3" t="s">
@@ -23770,18 +24111,20 @@
       <c r="L328" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M328" s="5"/>
-      <c r="N328" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O328" s="10">
+      <c r="M328" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N328" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O328" s="9">
         <v>46313</v>
       </c>
       <c r="P328" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="329" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
         <v>167</v>
       </c>
@@ -23818,18 +24161,20 @@
       <c r="L329" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M329" s="5"/>
-      <c r="N329" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O329" s="10">
+      <c r="M329" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N329" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O329" s="9">
         <v>46313</v>
       </c>
       <c r="P329" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
         <v>167</v>
       </c>
@@ -23866,11 +24211,13 @@
       <c r="L330" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M330" s="5"/>
-      <c r="N330" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O330" s="10">
+      <c r="M330" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N330" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O330" s="9">
         <v>46313</v>
       </c>
       <c r="P330" s="3" t="s">
@@ -23927,7 +24274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
         <v>167</v>
       </c>
@@ -23964,11 +24311,13 @@
       <c r="L332" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M332" s="5"/>
-      <c r="N332" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O332" s="10">
+      <c r="M332" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N332" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O332" s="9">
         <v>46313</v>
       </c>
       <c r="P332" s="3" t="s">
@@ -24025,7 +24374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="334" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A334" s="3" t="s">
         <v>167</v>
       </c>
@@ -24062,18 +24411,20 @@
       <c r="L334" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M334" s="5"/>
-      <c r="N334" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O334" s="10">
+      <c r="M334" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N334" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O334" s="9">
         <v>46313</v>
       </c>
       <c r="P334" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="335" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
         <v>167</v>
       </c>
@@ -24110,18 +24461,20 @@
       <c r="L335" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M335" s="5"/>
-      <c r="N335" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O335" s="10">
+      <c r="M335" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N335" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O335" s="9">
         <v>46313</v>
       </c>
       <c r="P335" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="336" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
         <v>167</v>
       </c>
@@ -24158,18 +24511,20 @@
       <c r="L336" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M336" s="5"/>
-      <c r="N336" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O336" s="10">
+      <c r="M336" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N336" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O336" s="9">
         <v>46313</v>
       </c>
       <c r="P336" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="337" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
         <v>167</v>
       </c>
@@ -24206,11 +24561,13 @@
       <c r="L337" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M337" s="5"/>
-      <c r="N337" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O337" s="10">
+      <c r="M337" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N337" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O337" s="9">
         <v>46313</v>
       </c>
       <c r="P337" s="3" t="s">
@@ -24254,18 +24611,20 @@
       <c r="L338" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M338" s="5"/>
-      <c r="N338" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O338" s="10">
+      <c r="M338" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N338" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O338" s="9">
         <v>46313</v>
       </c>
       <c r="P338" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="339" spans="1:16" ht="144" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:16" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
         <v>167</v>
       </c>
@@ -24302,18 +24661,20 @@
       <c r="L339" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M339" s="5"/>
-      <c r="N339" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O339" s="10">
+      <c r="M339" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N339" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O339" s="9">
         <v>46313</v>
       </c>
       <c r="P339" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
         <v>167</v>
       </c>
@@ -24350,18 +24711,20 @@
       <c r="L340" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M340" s="5"/>
-      <c r="N340" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O340" s="10">
+      <c r="M340" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N340" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O340" s="9">
         <v>46313</v>
       </c>
       <c r="P340" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
         <v>167</v>
       </c>
@@ -24398,18 +24761,20 @@
       <c r="L341" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M341" s="5"/>
-      <c r="N341" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O341" s="10">
+      <c r="M341" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N341" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O341" s="9">
         <v>46313</v>
       </c>
       <c r="P341" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="342" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A342" s="3" t="s">
         <v>167</v>
       </c>
@@ -24446,18 +24811,20 @@
       <c r="L342" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M342" s="5"/>
-      <c r="N342" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O342" s="10">
+      <c r="M342" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N342" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O342" s="9">
         <v>46313</v>
       </c>
       <c r="P342" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="343" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
         <v>167</v>
       </c>
@@ -24494,18 +24861,20 @@
       <c r="L343" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M343" s="5"/>
-      <c r="N343" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O343" s="10">
+      <c r="M343" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N343" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O343" s="9">
         <v>46313</v>
       </c>
       <c r="P343" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A344" s="3" t="s">
         <v>167</v>
       </c>
@@ -24542,11 +24911,13 @@
       <c r="L344" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M344" s="5"/>
-      <c r="N344" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O344" s="10">
+      <c r="M344" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N344" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O344" s="9">
         <v>46313</v>
       </c>
       <c r="P344" s="3" t="s">
@@ -24590,11 +24961,13 @@
       <c r="L345" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M345" s="5"/>
-      <c r="N345" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O345" s="10">
+      <c r="M345" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N345" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O345" s="9">
         <v>46313</v>
       </c>
       <c r="P345" s="3" t="s">
@@ -24638,18 +25011,20 @@
       <c r="L346" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M346" s="5"/>
-      <c r="N346" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O346" s="10">
+      <c r="M346" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N346" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O346" s="9">
         <v>46313</v>
       </c>
       <c r="P346" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="347" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
         <v>167</v>
       </c>
@@ -24686,18 +25061,20 @@
       <c r="L347" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M347" s="5"/>
-      <c r="N347" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O347" s="10">
+      <c r="M347" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N347" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O347" s="9">
         <v>46313</v>
       </c>
       <c r="P347" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="348" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
         <v>167</v>
       </c>
@@ -24734,18 +25111,20 @@
       <c r="L348" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M348" s="5"/>
-      <c r="N348" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O348" s="10">
+      <c r="M348" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N348" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O348" s="9">
         <v>46313</v>
       </c>
       <c r="P348" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="349" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
         <v>167</v>
       </c>
@@ -24782,11 +25161,13 @@
       <c r="L349" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M349" s="5"/>
-      <c r="N349" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O349" s="10">
+      <c r="M349" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N349" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O349" s="9">
         <v>46313</v>
       </c>
       <c r="P349" s="3" t="s">
@@ -24830,18 +25211,20 @@
       <c r="L350" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M350" s="5"/>
-      <c r="N350" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O350" s="10">
+      <c r="M350" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N350" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O350" s="9">
         <v>46313</v>
       </c>
       <c r="P350" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
         <v>167</v>
       </c>
@@ -24878,18 +25261,20 @@
       <c r="L351" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M351" s="5"/>
-      <c r="N351" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O351" s="10">
+      <c r="M351" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N351" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O351" s="9">
         <v>46313</v>
       </c>
       <c r="P351" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="352" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A352" s="3" t="s">
         <v>167</v>
       </c>
@@ -24926,18 +25311,20 @@
       <c r="L352" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M352" s="5"/>
-      <c r="N352" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O352" s="10">
+      <c r="M352" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N352" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O352" s="9">
         <v>46313</v>
       </c>
       <c r="P352" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="353" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
         <v>167</v>
       </c>
@@ -24974,18 +25361,20 @@
       <c r="L353" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M353" s="5"/>
-      <c r="N353" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O353" s="10">
+      <c r="M353" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N353" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O353" s="9">
         <v>46313</v>
       </c>
       <c r="P353" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="354" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
         <v>167</v>
       </c>
@@ -25022,18 +25411,20 @@
       <c r="L354" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M354" s="5"/>
-      <c r="N354" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O354" s="10">
+      <c r="M354" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N354" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O354" s="9">
         <v>46313</v>
       </c>
       <c r="P354" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
         <v>167</v>
       </c>
@@ -25070,18 +25461,20 @@
       <c r="L355" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M355" s="5"/>
-      <c r="N355" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O355" s="10">
+      <c r="M355" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N355" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O355" s="9">
         <v>46313</v>
       </c>
       <c r="P355" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="356" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
         <v>167</v>
       </c>
@@ -25118,11 +25511,13 @@
       <c r="L356" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M356" s="5"/>
-      <c r="N356" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O356" s="10">
+      <c r="M356" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N356" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O356" s="9">
         <v>46313</v>
       </c>
       <c r="P356" s="3" t="s">
@@ -25166,18 +25561,20 @@
       <c r="L357" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M357" s="5"/>
-      <c r="N357" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O357" s="10">
+      <c r="M357" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N357" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O357" s="9">
         <v>46313</v>
       </c>
       <c r="P357" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A358" s="3" t="s">
         <v>167</v>
       </c>
@@ -25214,18 +25611,20 @@
       <c r="L358" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M358" s="5"/>
-      <c r="N358" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O358" s="10">
+      <c r="M358" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N358" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O358" s="9">
         <v>46313</v>
       </c>
       <c r="P358" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
         <v>167</v>
       </c>
@@ -25262,18 +25661,20 @@
       <c r="L359" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M359" s="5"/>
-      <c r="N359" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O359" s="10">
+      <c r="M359" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N359" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O359" s="9">
         <v>46313</v>
       </c>
       <c r="P359" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
         <v>167</v>
       </c>
@@ -25310,18 +25711,20 @@
       <c r="L360" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M360" s="5"/>
-      <c r="N360" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O360" s="10">
+      <c r="M360" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N360" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O360" s="9">
         <v>46313</v>
       </c>
       <c r="P360" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="361" spans="1:16" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:16" ht="144" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
         <v>167</v>
       </c>
@@ -25358,11 +25761,13 @@
       <c r="L361" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M361" s="5"/>
-      <c r="N361" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O361" s="10">
+      <c r="M361" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N361" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O361" s="9">
         <v>46313</v>
       </c>
       <c r="P361" s="3" t="s">
@@ -25406,11 +25811,13 @@
       <c r="L362" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M362" s="5"/>
-      <c r="N362" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O362" s="10">
+      <c r="M362" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="N362" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O362" s="9">
         <v>46313</v>
       </c>
       <c r="P362" s="3" t="s">
@@ -25454,18 +25861,20 @@
       <c r="L363" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M363" s="5"/>
-      <c r="N363" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O363" s="10">
+      <c r="M363" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N363" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O363" s="9">
         <v>46313</v>
       </c>
       <c r="P363" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="364" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
         <v>167</v>
       </c>
@@ -25502,18 +25911,20 @@
       <c r="L364" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M364" s="5"/>
-      <c r="N364" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O364" s="10">
+      <c r="M364" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N364" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O364" s="9">
         <v>46313</v>
       </c>
       <c r="P364" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="365" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
         <v>167</v>
       </c>
@@ -25550,11 +25961,13 @@
       <c r="L365" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M365" s="5"/>
-      <c r="N365" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O365" s="10">
+      <c r="M365" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="N365" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O365" s="9">
         <v>46313</v>
       </c>
       <c r="P365" s="3" t="s">
@@ -25611,7 +26024,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
         <v>167</v>
       </c>
@@ -25648,18 +26061,20 @@
       <c r="L367" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M367" s="5"/>
-      <c r="N367" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O367" s="10">
+      <c r="M367" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N367" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O367" s="9">
         <v>46313</v>
       </c>
       <c r="P367" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="368" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
         <v>167</v>
       </c>
@@ -25696,18 +26111,20 @@
       <c r="L368" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M368" s="5"/>
-      <c r="N368" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O368" s="10">
+      <c r="M368" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N368" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O368" s="9">
         <v>46313</v>
       </c>
       <c r="P368" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
         <v>167</v>
       </c>
@@ -25744,18 +26161,20 @@
       <c r="L369" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M369" s="5"/>
-      <c r="N369" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O369" s="10">
+      <c r="M369" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N369" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O369" s="9">
         <v>46313</v>
       </c>
       <c r="P369" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="370" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A370" s="3" t="s">
         <v>167</v>
       </c>
@@ -25792,18 +26211,20 @@
       <c r="L370" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M370" s="5"/>
-      <c r="N370" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O370" s="10">
+      <c r="M370" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N370" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O370" s="9">
         <v>46313</v>
       </c>
       <c r="P370" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="371" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
         <v>167</v>
       </c>
@@ -25840,18 +26261,20 @@
       <c r="L371" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M371" s="5"/>
-      <c r="N371" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O371" s="10">
+      <c r="M371" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N371" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O371" s="9">
         <v>46313</v>
       </c>
       <c r="P371" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="372" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A372" s="3" t="s">
         <v>167</v>
       </c>
@@ -25888,11 +26311,13 @@
       <c r="L372" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M372" s="5"/>
-      <c r="N372" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O372" s="10">
+      <c r="M372" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N372" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O372" s="9">
         <v>46313</v>
       </c>
       <c r="P372" s="3" t="s">
@@ -25936,11 +26361,13 @@
       <c r="L373" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M373" s="5"/>
-      <c r="N373" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O373" s="10">
+      <c r="M373" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="N373" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O373" s="9">
         <v>46313</v>
       </c>
       <c r="P373" s="3" t="s">
@@ -25984,11 +26411,13 @@
       <c r="L374" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M374" s="5"/>
-      <c r="N374" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O374" s="10">
+      <c r="M374" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="N374" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O374" s="9">
         <v>46313</v>
       </c>
       <c r="P374" s="3" t="s">
@@ -26032,18 +26461,20 @@
       <c r="L375" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M375" s="5"/>
-      <c r="N375" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O375" s="10">
+      <c r="M375" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="N375" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O375" s="9">
         <v>46313</v>
       </c>
       <c r="P375" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
         <v>47</v>
       </c>
@@ -26080,18 +26511,20 @@
       <c r="L376" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M376" s="5"/>
-      <c r="N376" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O376" s="10">
+      <c r="M376" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="N376" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O376" s="9">
         <v>46313</v>
       </c>
       <c r="P376" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="377" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
         <v>167</v>
       </c>
@@ -26128,11 +26561,13 @@
       <c r="L377" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M377" s="5"/>
-      <c r="N377" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O377" s="10">
+      <c r="M377" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N377" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O377" s="9">
         <v>46313</v>
       </c>
       <c r="P377" s="3" t="s">
@@ -26176,18 +26611,20 @@
       <c r="L378" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M378" s="5"/>
-      <c r="N378" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O378" s="10">
+      <c r="M378" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N378" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O378" s="9">
         <v>46313</v>
       </c>
       <c r="P378" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
         <v>167</v>
       </c>
@@ -26224,11 +26661,13 @@
       <c r="L379" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M379" s="5"/>
-      <c r="N379" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O379" s="10">
+      <c r="M379" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N379" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O379" s="9">
         <v>46313</v>
       </c>
       <c r="P379" s="3" t="s">
@@ -26272,18 +26711,20 @@
       <c r="L380" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M380" s="5"/>
-      <c r="N380" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O380" s="10">
+      <c r="M380" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N380" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O380" s="9">
         <v>46313</v>
       </c>
       <c r="P380" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
         <v>34</v>
       </c>
@@ -26370,11 +26811,13 @@
       <c r="L382" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M382" s="5"/>
-      <c r="N382" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O382" s="10">
+      <c r="M382" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="N382" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O382" s="9">
         <v>46313</v>
       </c>
       <c r="P382" s="3" t="s">

--- a/03_Labeling/outputs/full_annotation/full_annotation_381.xlsx
+++ b/03_Labeling/outputs/full_annotation/full_annotation_381.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Penelitian Sentimen Bencana Nasional\03_Labeling\outputs\full_annotation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A9B290-41C0-4EE3-A833-3A941ADDFEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4066B7B-E111-4FFC-8F32-F1F957C8D4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7874,7 +7874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>47</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>167</v>
       </c>
@@ -9424,7 +9424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>47</v>
       </c>
@@ -9524,7 +9524,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>47</v>
       </c>
@@ -11174,7 +11174,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>34</v>
       </c>
@@ -13924,7 +13924,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>167</v>
       </c>
@@ -14074,7 +14074,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>167</v>
       </c>
@@ -14174,7 +14174,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>167</v>
       </c>
@@ -22174,7 +22174,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>47</v>
       </c>
@@ -25974,7 +25974,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="366" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
         <v>167</v>
       </c>
